--- a/mode_docx_gen/pmi_ka/ksv1_modes/КСВ_14.xlsx
+++ b/mode_docx_gen/pmi_ka/ksv1_modes/КСВ_14.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>SGF13_tsa</t>
+          <t>SGF13_lvalh</t>
         </is>
       </c>
     </row>
@@ -1152,8 +1152,8 @@
       <c r="U2" t="n">
         <v>0</v>
       </c>
-      <c r="V2" t="n">
-        <v>0</v>
+      <c r="V2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
